--- a/AVI_respostas 1_2_3_4 semestre_2026_1.xlsx
+++ b/AVI_respostas 1_2_3_4 semestre_2026_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orlandoalbarracin/Documents/Mackenzie/Mackenzie 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94013AAF-BF10-A342-B0D3-9845F429F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F314604E-58A8-5946-985F-6864C4648E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{CB971484-1340-DE40-A32A-2CEEFCF8A695}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CB971484-1340-DE40-A32A-2CEEFCF8A695}"/>
   </bookViews>
   <sheets>
     <sheet name="Basico 1 sem" sheetId="3" r:id="rId1"/>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>MATEMATICA</t>
+  </si>
+  <si>
+    <t>FISICA</t>
   </si>
   <si>
     <t>Difícil</t>
@@ -327,9 +330,6 @@
   </si>
   <si>
     <t>não registrado</t>
-  </si>
-  <si>
-    <t>FISCA</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -675,9 +675,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -688,9 +685,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1034,9 +1028,9 @@
   <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="9" max="9" width="17" style="53" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" style="53" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="64.83203125" style="53" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="51" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" style="51" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="64.83203125" style="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -1106,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1141,7 +1135,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1176,7 +1170,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1211,7 +1205,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1246,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1281,7 +1275,7 @@
         <v>15</v>
       </c>
       <c r="K7" s="45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1316,7 +1310,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1351,7 +1345,7 @@
         <v>24</v>
       </c>
       <c r="K9" s="45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1386,7 +1380,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1421,7 +1415,7 @@
         <v>24</v>
       </c>
       <c r="K11" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1456,7 +1450,7 @@
         <v>24</v>
       </c>
       <c r="K12" s="45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1491,7 +1485,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1526,7 +1520,7 @@
         <v>15</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -1561,7 +1555,7 @@
         <v>15</v>
       </c>
       <c r="K15" s="45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -1596,7 +1590,7 @@
         <v>15</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -1628,10 +1622,10 @@
         <v>35</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -1666,7 +1660,7 @@
         <v>24</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -1701,7 +1695,7 @@
         <v>24</v>
       </c>
       <c r="K19" s="45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -1730,7 +1724,7 @@
         <v>20</v>
       </c>
       <c r="I20" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J20" s="44" t="s">
         <v>13</v>
@@ -1765,7 +1759,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J21" s="44" t="s">
         <v>13</v>
@@ -1800,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J22" s="44" t="s">
         <v>13</v>
@@ -1835,7 +1829,7 @@
         <v>241</v>
       </c>
       <c r="I23" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J23" s="44" t="s">
         <v>13</v>
@@ -1870,7 +1864,7 @@
         <v>51</v>
       </c>
       <c r="I24" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J24" s="44" t="s">
         <v>13</v>
@@ -1905,7 +1899,7 @@
         <v>35</v>
       </c>
       <c r="I25" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J25" s="44" t="s">
         <v>13</v>
@@ -1940,7 +1934,7 @@
         <v>19</v>
       </c>
       <c r="I26" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J26" s="44" t="s">
         <v>13</v>
@@ -1975,7 +1969,7 @@
         <v>78</v>
       </c>
       <c r="I27" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J27" s="44" t="s">
         <v>13</v>
@@ -2010,7 +2004,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J28" s="44" t="s">
         <v>13</v>
@@ -2045,7 +2039,7 @@
         <v>81</v>
       </c>
       <c r="I29" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J29" s="44" t="s">
         <v>13</v>
@@ -2080,7 +2074,7 @@
         <v>30</v>
       </c>
       <c r="I30" s="43" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J30" s="44" t="s">
         <v>13</v>
@@ -2114,13 +2108,13 @@
       <c r="H31" s="10">
         <v>14</v>
       </c>
-      <c r="I31" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="J31" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="47" t="s">
+      <c r="I31" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J31" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="46" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2149,14 +2143,14 @@
       <c r="H32" s="10">
         <v>3</v>
       </c>
-      <c r="I32" s="48" t="s">
+      <c r="I32" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="J32" s="49" t="s">
+      <c r="J32" s="48" t="s">
         <v>13</v>
       </c>
       <c r="K32" s="45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -2184,14 +2178,14 @@
       <c r="H33" s="10">
         <v>1</v>
       </c>
-      <c r="I33" s="48" t="s">
+      <c r="I33" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K33" s="50" t="s">
-        <v>40</v>
+      <c r="J33" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="49" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -2219,14 +2213,14 @@
       <c r="H34" s="10">
         <v>5</v>
       </c>
-      <c r="I34" s="48" t="s">
+      <c r="I34" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="J34" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="50" t="s">
-        <v>38</v>
+      <c r="J34" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -2254,14 +2248,14 @@
       <c r="H35" s="10">
         <v>0</v>
       </c>
-      <c r="I35" s="48" t="s">
+      <c r="I35" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="J35" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="50" t="s">
-        <v>39</v>
+      <c r="J35" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="49" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -2289,14 +2283,14 @@
       <c r="H36" s="10">
         <v>23</v>
       </c>
-      <c r="I36" s="48" t="s">
+      <c r="I36" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="J36" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K36" s="50" t="s">
-        <v>37</v>
+      <c r="J36" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="49" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2324,14 +2318,14 @@
       <c r="H37" s="10">
         <v>8</v>
       </c>
-      <c r="I37" s="48" t="s">
+      <c r="I37" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="50" t="s">
+      <c r="J37" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="K37" s="50" t="s">
-        <v>45</v>
+      <c r="K37" s="49" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -2359,14 +2353,14 @@
       <c r="H38" s="10">
         <v>37</v>
       </c>
-      <c r="I38" s="48" t="s">
+      <c r="I38" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J38" s="50" t="s">
+      <c r="J38" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K38" s="50" t="s">
-        <v>44</v>
+      <c r="K38" s="49" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -2394,14 +2388,14 @@
       <c r="H39" s="10">
         <v>119</v>
       </c>
-      <c r="I39" s="48" t="s">
+      <c r="I39" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J39" s="50" t="s">
+      <c r="J39" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K39" s="50" t="s">
-        <v>42</v>
+      <c r="K39" s="49" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -2429,14 +2423,14 @@
       <c r="H40" s="10">
         <v>105</v>
       </c>
-      <c r="I40" s="48" t="s">
+      <c r="I40" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J40" s="50" t="s">
+      <c r="J40" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="K40" s="50" t="s">
-        <v>47</v>
+      <c r="K40" s="49" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -2464,14 +2458,14 @@
       <c r="H41" s="10">
         <v>39</v>
       </c>
-      <c r="I41" s="48" t="s">
+      <c r="I41" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J41" s="50" t="s">
+      <c r="J41" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K41" s="50" t="s">
-        <v>46</v>
+      <c r="K41" s="49" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -2499,14 +2493,14 @@
       <c r="H42" s="10">
         <v>39</v>
       </c>
-      <c r="I42" s="48" t="s">
+      <c r="I42" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J42" s="50" t="s">
+      <c r="J42" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="50" t="s">
-        <v>48</v>
+      <c r="K42" s="49" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -2534,14 +2528,14 @@
       <c r="H43" s="10">
         <v>11</v>
       </c>
-      <c r="I43" s="48" t="s">
+      <c r="I43" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="50" t="s">
+      <c r="J43" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K43" s="50" t="s">
-        <v>49</v>
+      <c r="K43" s="49" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -2569,14 +2563,14 @@
       <c r="H44" s="10">
         <v>5</v>
       </c>
-      <c r="I44" s="48" t="s">
+      <c r="I44" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J44" s="50" t="s">
+      <c r="J44" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K44" s="50" t="s">
-        <v>50</v>
+      <c r="K44" s="49" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -2604,14 +2598,14 @@
       <c r="H45" s="10">
         <v>9</v>
       </c>
-      <c r="I45" s="48" t="s">
+      <c r="I45" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J45" s="50" t="s">
+      <c r="J45" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K45" s="50" t="s">
-        <v>46</v>
+      <c r="K45" s="49" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2639,14 +2633,14 @@
       <c r="H46" s="10">
         <v>7</v>
       </c>
-      <c r="I46" s="48" t="s">
+      <c r="I46" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J46" s="50" t="s">
+      <c r="J46" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="K46" s="50" t="s">
-        <v>51</v>
+      <c r="K46" s="49" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -2674,14 +2668,14 @@
       <c r="H47" s="10">
         <v>2</v>
       </c>
-      <c r="I47" s="48" t="s">
+      <c r="I47" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J47" s="50" t="s">
+      <c r="J47" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="50" t="s">
-        <v>53</v>
+      <c r="K47" s="49" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2709,14 +2703,14 @@
       <c r="H48" s="10">
         <v>5</v>
       </c>
-      <c r="I48" s="48" t="s">
+      <c r="I48" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J48" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="K48" s="50" t="s">
-        <v>52</v>
+      <c r="J48" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" s="49" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -2744,14 +2738,14 @@
       <c r="H49" s="10">
         <v>14</v>
       </c>
-      <c r="I49" s="48" t="s">
+      <c r="I49" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J49" s="50" t="s">
+      <c r="J49" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="K49" s="50" t="s">
-        <v>54</v>
+      <c r="K49" s="49" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -2779,13 +2773,13 @@
       <c r="H50" s="10">
         <v>3</v>
       </c>
-      <c r="I50" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J50" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K50" s="49" t="s">
+      <c r="I50" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2814,13 +2808,13 @@
       <c r="H51" s="10">
         <v>18</v>
       </c>
-      <c r="I51" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J51" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K51" s="49" t="s">
+      <c r="I51" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2849,13 +2843,13 @@
       <c r="H52" s="10">
         <v>6</v>
       </c>
-      <c r="I52" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J52" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K52" s="49" t="s">
+      <c r="I52" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J52" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K52" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2884,13 +2878,13 @@
       <c r="H53" s="10">
         <v>126</v>
       </c>
-      <c r="I53" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J53" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K53" s="49" t="s">
+      <c r="I53" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J53" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2919,13 +2913,13 @@
       <c r="H54" s="10">
         <v>33</v>
       </c>
-      <c r="I54" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J54" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K54" s="49" t="s">
+      <c r="I54" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K54" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2954,13 +2948,13 @@
       <c r="H55" s="10">
         <v>8</v>
       </c>
-      <c r="I55" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J55" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K55" s="49" t="s">
+      <c r="I55" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J55" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K55" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2989,13 +2983,13 @@
       <c r="H56" s="10">
         <v>25</v>
       </c>
-      <c r="I56" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J56" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K56" s="49" t="s">
+      <c r="I56" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J56" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3024,13 +3018,13 @@
       <c r="H57" s="10">
         <v>50</v>
       </c>
-      <c r="I57" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J57" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K57" s="49" t="s">
+      <c r="I57" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K57" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3059,13 +3053,13 @@
       <c r="H58" s="10">
         <v>46</v>
       </c>
-      <c r="I58" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J58" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K58" s="49" t="s">
+      <c r="I58" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J58" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3094,13 +3088,13 @@
       <c r="H59" s="10">
         <v>6</v>
       </c>
-      <c r="I59" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J59" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K59" s="49" t="s">
+      <c r="I59" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J59" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K59" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3129,13 +3123,13 @@
       <c r="H60" s="10">
         <v>15</v>
       </c>
-      <c r="I60" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="J60" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K60" s="49" t="s">
+      <c r="I60" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J60" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K60" s="48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3164,13 +3158,13 @@
       <c r="H61" s="10">
         <v>8</v>
       </c>
-      <c r="I61" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="J61" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="K61" s="52" t="s">
+      <c r="I61" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J61" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="K61" s="50" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3359,10 +3353,10 @@
         <v>14</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -3394,10 +3388,10 @@
         <v>14</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -3429,7 +3423,7 @@
         <v>14</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
         <v>29</v>
@@ -3467,7 +3461,7 @@
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -3499,10 +3493,10 @@
         <v>31</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -3534,10 +3528,10 @@
         <v>31</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -3569,10 +3563,10 @@
         <v>31</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -3604,10 +3598,10 @@
         <v>31</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -3747,7 +3741,7 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -3779,10 +3773,10 @@
         <v>32</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -3814,10 +3808,10 @@
         <v>16</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -3849,10 +3843,10 @@
         <v>16</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -3884,10 +3878,10 @@
         <v>16</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -3922,7 +3916,7 @@
         <v>24</v>
       </c>
       <c r="K21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -3954,10 +3948,10 @@
         <v>16</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -4132,7 +4126,7 @@
         <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -4167,7 +4161,7 @@
         <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -4202,7 +4196,7 @@
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -4237,7 +4231,7 @@
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -4272,7 +4266,7 @@
         <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -4307,7 +4301,7 @@
         <v>13</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -4342,7 +4336,7 @@
         <v>13</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -4377,7 +4371,7 @@
         <v>13</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -4412,7 +4406,7 @@
         <v>13</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -4447,7 +4441,7 @@
         <v>13</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -4619,10 +4613,10 @@
         <v>16</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -4654,10 +4648,10 @@
         <v>16</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -4689,10 +4683,10 @@
         <v>16</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -4727,7 +4721,7 @@
         <v>24</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -4759,10 +4753,10 @@
         <v>16</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -4902,7 +4896,7 @@
         <v>24</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -4934,10 +4928,10 @@
         <v>32</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -4972,7 +4966,7 @@
         <v>24</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -5004,10 +4998,10 @@
         <v>31</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -5039,10 +5033,10 @@
         <v>31</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -5074,10 +5068,10 @@
         <v>31</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -5109,10 +5103,10 @@
         <v>31</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -5144,10 +5138,10 @@
         <v>14</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -5179,10 +5173,10 @@
         <v>14</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -5214,7 +5208,7 @@
         <v>14</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>29</v>
@@ -5408,7 +5402,7 @@
         <v>24</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -5440,10 +5434,10 @@
         <v>17</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -5475,10 +5469,10 @@
         <v>17</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -5510,10 +5504,10 @@
         <v>17</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -5548,7 +5542,7 @@
         <v>24</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -5580,10 +5574,10 @@
         <v>18</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -5653,7 +5647,7 @@
         <v>24</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -5685,10 +5679,10 @@
         <v>18</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -5723,7 +5717,7 @@
         <v>24</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -5758,7 +5752,7 @@
         <v>24</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -5793,7 +5787,7 @@
         <v>24</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -5828,7 +5822,7 @@
         <v>24</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -5863,7 +5857,7 @@
         <v>24</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -5898,7 +5892,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -5933,7 +5927,7 @@
         <v>13</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -6003,7 +5997,7 @@
         <v>24</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -6038,7 +6032,7 @@
         <v>24</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -6070,10 +6064,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -6108,7 +6102,7 @@
         <v>24</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -6140,10 +6134,10 @@
         <v>14</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -6175,10 +6169,10 @@
         <v>14</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -6210,10 +6204,10 @@
         <v>16</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -6245,10 +6239,10 @@
         <v>16</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -6630,10 +6624,10 @@
         <v>14</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -6665,10 +6659,10 @@
         <v>14</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -6700,10 +6694,10 @@
         <v>16</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -6735,10 +6729,10 @@
         <v>16</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K40" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -6773,7 +6767,7 @@
         <v>24</v>
       </c>
       <c r="K41" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -6805,10 +6799,10 @@
         <v>17</v>
       </c>
       <c r="J42" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K42" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -6840,10 +6834,10 @@
         <v>17</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K43" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -6875,10 +6869,10 @@
         <v>17</v>
       </c>
       <c r="J44" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K44" s="34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -6913,7 +6907,7 @@
         <v>24</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -6945,10 +6939,10 @@
         <v>18</v>
       </c>
       <c r="J46" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K46" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -7018,7 +7012,7 @@
         <v>24</v>
       </c>
       <c r="K48" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -7050,10 +7044,10 @@
         <v>18</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K49" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -7088,7 +7082,7 @@
         <v>24</v>
       </c>
       <c r="K50" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -7123,7 +7117,7 @@
         <v>24</v>
       </c>
       <c r="K51" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -7158,7 +7152,7 @@
         <v>24</v>
       </c>
       <c r="K52" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -7193,7 +7187,7 @@
         <v>24</v>
       </c>
       <c r="K53" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -7228,7 +7222,7 @@
         <v>24</v>
       </c>
       <c r="K54" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -7263,7 +7257,7 @@
         <v>13</v>
       </c>
       <c r="K55" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -7298,7 +7292,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -7368,7 +7362,7 @@
         <v>24</v>
       </c>
       <c r="K58" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -7403,7 +7397,7 @@
         <v>24</v>
       </c>
       <c r="K59" s="21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -7435,10 +7429,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K60" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -7473,7 +7467,7 @@
         <v>24</v>
       </c>
       <c r="K61" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -7557,10 +7551,10 @@
         <v>12</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -7592,10 +7586,10 @@
         <v>12</v>
       </c>
       <c r="J3" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -7627,10 +7621,10 @@
         <v>12</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -7662,10 +7656,10 @@
         <v>12</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -7697,10 +7691,10 @@
         <v>12</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -7732,10 +7726,10 @@
         <v>25</v>
       </c>
       <c r="J7" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -7767,10 +7761,10 @@
         <v>25</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -7802,10 +7796,10 @@
         <v>25</v>
       </c>
       <c r="J9" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -7837,10 +7831,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -7872,10 +7866,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -7907,10 +7901,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -7942,10 +7936,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -7977,10 +7971,10 @@
         <v>14</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -8012,10 +8006,10 @@
         <v>14</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -8047,10 +8041,10 @@
         <v>14</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -8082,10 +8076,10 @@
         <v>17</v>
       </c>
       <c r="J17" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -8117,10 +8111,10 @@
         <v>17</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -8152,10 +8146,10 @@
         <v>17</v>
       </c>
       <c r="J19" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K19" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -8187,10 +8181,10 @@
         <v>26</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -8222,10 +8216,10 @@
         <v>26</v>
       </c>
       <c r="J21" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -8257,10 +8251,10 @@
         <v>26</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -8292,10 +8286,10 @@
         <v>26</v>
       </c>
       <c r="J23" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -8327,10 +8321,10 @@
         <v>27</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -8362,10 +8356,10 @@
         <v>27</v>
       </c>
       <c r="J25" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K25" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -8397,10 +8391,10 @@
         <v>27</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -8429,13 +8423,13 @@
         <v>6</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J27" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K27" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -8467,10 +8461,10 @@
         <v>21</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -8502,10 +8496,10 @@
         <v>28</v>
       </c>
       <c r="J29" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K29" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -8537,10 +8531,10 @@
         <v>28</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -8572,10 +8566,10 @@
         <v>28</v>
       </c>
       <c r="J31" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K31" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -8607,10 +8601,10 @@
         <v>25</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -8642,10 +8636,10 @@
         <v>25</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -8677,10 +8671,10 @@
         <v>25</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -8712,10 +8706,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -8747,10 +8741,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -8782,10 +8776,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K37" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -8817,10 +8811,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -8852,10 +8846,10 @@
         <v>14</v>
       </c>
       <c r="J39" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K39" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -8887,10 +8881,10 @@
         <v>14</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -8922,10 +8916,10 @@
         <v>14</v>
       </c>
       <c r="J41" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K41" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -8957,10 +8951,10 @@
         <v>17</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -8992,10 +8986,10 @@
         <v>17</v>
       </c>
       <c r="J43" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -9027,10 +9021,10 @@
         <v>17</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -9062,10 +9056,10 @@
         <v>26</v>
       </c>
       <c r="J45" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K45" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -9097,10 +9091,10 @@
         <v>26</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -9132,10 +9126,10 @@
         <v>26</v>
       </c>
       <c r="J47" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K47" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -9167,10 +9161,10 @@
         <v>26</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -9202,10 +9196,10 @@
         <v>27</v>
       </c>
       <c r="J49" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K49" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -9237,10 +9231,10 @@
         <v>27</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -9272,10 +9266,10 @@
         <v>27</v>
       </c>
       <c r="J51" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -9304,13 +9298,13 @@
         <v>15</v>
       </c>
       <c r="I52" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -9342,10 +9336,10 @@
         <v>21</v>
       </c>
       <c r="J53" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K53" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -9377,10 +9371,10 @@
         <v>28</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -9412,10 +9406,10 @@
         <v>28</v>
       </c>
       <c r="J55" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K55" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -9447,10 +9441,10 @@
         <v>28</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -9482,10 +9476,10 @@
         <v>12</v>
       </c>
       <c r="J57" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K57" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -9517,10 +9511,10 @@
         <v>12</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -9552,10 +9546,10 @@
         <v>12</v>
       </c>
       <c r="J59" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K59" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -9587,10 +9581,10 @@
         <v>12</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -9622,10 +9616,10 @@
         <v>12</v>
       </c>
       <c r="J61" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K61" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
